--- a/TestCases.xlsx
+++ b/TestCases.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/grigorijkajgorodcev/Desktop/Новая папка/Диплом/Plan/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EA1632F9-A1C5-5445-9FBF-10BADE7C9AD4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E276846A-5C66-3042-933B-4FB2C4934F8A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="12340" yWindow="500" windowWidth="16180" windowHeight="16260" xr2:uid="{5EBC1BF0-8D22-3E49-86A7-6D4B75A50D4A}"/>
   </bookViews>
